--- a/content/Notes/Biology/Labs/Lab 06/Lab 07/BIOL 1400 F25 Fermentation Analyses Expt Data Template.xlsx
+++ b/content/Notes/Biology/Labs/Lab 06/Lab 07/BIOL 1400 F25 Fermentation Analyses Expt Data Template.xlsx
@@ -8,14 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gassandrid/VAULT/Notes/Biology/Labs/Lab 06/Lab 07/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1661E2D0-6D16-9F41-BCC0-4B82063AAF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972F44EB-6764-A046-BA48-75232BF58AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25660" yWindow="740" windowWidth="25480" windowHeight="28000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="740" windowWidth="34440" windowHeight="21540" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Averages and T-Tests" sheetId="2" r:id="rId2"/>
+    <sheet name="Chart1" sheetId="3" r:id="rId1"/>
+    <sheet name="Chart2" sheetId="4" r:id="rId2"/>
+    <sheet name="Raw Data" sheetId="1" r:id="rId3"/>
+    <sheet name="Chart3" sheetId="5" r:id="rId4"/>
+    <sheet name="Averages and T-Tests" sheetId="2" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v2.0" hidden="1">'Averages and T-Tests'!$F$10:$F$12</definedName>
+    <definedName name="_xlchart.v2.1" hidden="1">'Averages and T-Tests'!$G$10:$G$12</definedName>
+  </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="33">
   <si>
     <t>Replicate A</t>
   </si>
@@ -63,9 +70,6 @@
     <t>t-test p-value</t>
   </si>
   <si>
-    <t xml:space="preserve"> ----</t>
-  </si>
-  <si>
     <t>Control Condition</t>
   </si>
   <si>
@@ -73,12 +77,6 @@
   </si>
   <si>
     <t xml:space="preserve">Condition #2: </t>
-  </si>
-  <si>
-    <t>Experimental Condition #1</t>
-  </si>
-  <si>
-    <t>Experimental Condition #2</t>
   </si>
   <si>
     <t>Condition #1</t>
@@ -611,14 +609,19 @@
   <si>
     <t>this value was a FAIL, but for sake of visualization I am going to make it the average of the other replicates</t>
   </si>
+  <si>
+    <t>Glucose 10%</t>
+  </si>
+  <si>
+    <t>Glucose 2.5%</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -732,7 +735,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -744,6 +747,19 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -775,26 +791,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -816,6 +832,4464 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Glucose</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> at 10%</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Raw Data'!$L$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Replicate A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:intercept val="0"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.10218349596010691"/>
+                  <c:y val="4.4445654257171799E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>Replicate A</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr/>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>y = 0.0281x</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" baseline="0"/>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>R² = 0.7254</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$M$10:$P$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$M$11:$P$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.88</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-98B7-F64E-9D7D-4211ED143276}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Raw Data'!$L$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Replicate B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:intercept val="0"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-8.75365913123788E-2"/>
+                  <c:y val="3.6883369595877976E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>Replicate B</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr/>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>y = 0.0177x</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" baseline="0"/>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>R² = 0.9166</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$M$10:$P$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$M$12:$P$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.38</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-98B7-F64E-9D7D-4211ED143276}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Raw Data'!$L$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Replicate C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:intercept val="0"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.1198538907829913E-3"/>
+                  <c:y val="-4.2809860101076673E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>Replicate C</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr/>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>y = 0.0177x</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" baseline="0"/>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>R² = 0.9068</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:solidFill>
+                    <a:schemeClr val="accent3"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$M$10:$P$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$M$13:$P$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.41</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-98B7-F64E-9D7D-4211ED143276}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Raw Data'!$L$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Replicate D</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:intercept val="0"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.0597669827399491E-2"/>
+                  <c:y val="7.2143043162934392E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>Replicate D</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr/>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>y = 0.0171x</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" baseline="0"/>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>R² = 0.9523</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:solidFill>
+                    <a:srgbClr val="7030A0"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$M$10:$P$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$M$14:$P$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.39</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-98B7-F64E-9D7D-4211ED143276}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1595986608"/>
+        <c:axId val="1595989568"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1595986608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                  <a:lnSpc>
+                    <a:spcPct val="100000"/>
+                  </a:lnSpc>
+                  <a:spcBef>
+                    <a:spcPts val="0"/>
+                  </a:spcBef>
+                  <a:spcAft>
+                    <a:spcPts val="0"/>
+                  </a:spcAft>
+                  <a:buClrTx/>
+                  <a:buSzTx/>
+                  <a:buFontTx/>
+                  <a:buNone/>
+                  <a:tabLst/>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Time Trial Length(in Minutes)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                <a:lnSpc>
+                  <a:spcPct val="100000"/>
+                </a:lnSpc>
+                <a:spcBef>
+                  <a:spcPts val="0"/>
+                </a:spcBef>
+                <a:spcAft>
+                  <a:spcPts val="0"/>
+                </a:spcAft>
+                <a:buClrTx/>
+                <a:buSzTx/>
+                <a:buFontTx/>
+                <a:buNone/>
+                <a:tabLst/>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1595989568"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1595989568"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Volume</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> CO2 Produced(in mLs)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1595986608"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="6"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="7"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Glucose</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> at 2.5%</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Raw Data'!$R$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Replicate A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:intercept val="0"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.3090210862375147E-2"/>
+                  <c:y val="7.6759433833113342E-4"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>Replicate A</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr/>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>y = 0.0321x</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" baseline="0"/>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>R² = 0.9374</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$S$10:$V$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$S$11:$V$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7F70-6749-A2B3-9913589DB3DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Raw Data'!$R$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Replicate B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:intercept val="0"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.3527050756945113E-2"/>
+                  <c:y val="0.10763289951995904"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>Replicate B</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr/>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>y = 0.0235x</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" baseline="0"/>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>R² = 0.8644</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$S$10:$V$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$S$12:$V$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.44</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7F70-6749-A2B3-9913589DB3DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Raw Data'!$R$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Replicate C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:intercept val="0"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.090281213649439E-2"/>
+                  <c:y val="-2.6467837128643207E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>Replicate C</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr/>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>y = 0.0259x</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" baseline="0"/>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>R² = 0.8951</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:solidFill>
+                    <a:schemeClr val="accent3"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$S$10:$V$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$S$13:$V$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.19</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7F70-6749-A2B3-9913589DB3DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Raw Data'!$R$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Replicate D</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:intercept val="0"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.0413663186239198E-2"/>
+                  <c:y val="0.15076797638445555"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>Replicate D</a:t>
+                    </a:r>
+                  </a:p>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr/>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>y = 0.0303x</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" baseline="0"/>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>R² = 0.9696</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:solidFill>
+                    <a:schemeClr val="accent4"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$S$10:$V$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Raw Data'!$S$14:$V$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.28999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.46</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7F70-6749-A2B3-9913589DB3DB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1478278655"/>
+        <c:axId val="1608588832"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1478278655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time Trial Length(in Minutes)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1608588832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1608588832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                  <a:lnSpc>
+                    <a:spcPct val="100000"/>
+                  </a:lnSpc>
+                  <a:spcBef>
+                    <a:spcPts val="0"/>
+                  </a:spcBef>
+                  <a:spcAft>
+                    <a:spcPts val="0"/>
+                  </a:spcAft>
+                  <a:buClrTx/>
+                  <a:buSzTx/>
+                  <a:buFontTx/>
+                  <a:buNone/>
+                  <a:tabLst/>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Volume CO2 Produced(in mLs)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                <a:lnSpc>
+                  <a:spcPct val="100000"/>
+                </a:lnSpc>
+                <a:spcBef>
+                  <a:spcPts val="0"/>
+                </a:spcBef>
+                <a:spcAft>
+                  <a:spcPts val="0"/>
+                </a:spcAft>
+                <a:buClrTx/>
+                <a:buSzTx/>
+                <a:buFontTx/>
+                <a:buNone/>
+                <a:tabLst/>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1478278655"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="6"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="7"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:errBars>
+            <c:errBarType val="both"/>
+            <c:errValType val="cust"/>
+            <c:noEndCap val="0"/>
+            <c:plus>
+              <c:numRef>
+                <c:f>'Averages and T-Tests'!$H$10:$H$12</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="3"/>
+                  <c:pt idx="0">
+                    <c:v>1E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>5.0000000000000001E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>3.0000000000000001E-3</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:plus>
+            <c:minus>
+              <c:numRef>
+                <c:f>'Averages and T-Tests'!$H$10:$H$12</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="3"/>
+                  <c:pt idx="0">
+                    <c:v>1E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>5.0000000000000001E-3</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>3.0000000000000001E-3</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:minus>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Averages and T-Tests'!$F$10:$F$12</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Control Condition</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Glucose 10%</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Glucose 2.5%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Averages and T-Tests'!$G$10:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-392B-0B41-A0F2-0A39AFCDE6DE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="1593354528"/>
+        <c:axId val="237566096"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1593354528"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="237566096"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="237566096"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1593354528"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="207">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700">
+        <a:solidFill>
+          <a:schemeClr val="lt2"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{A0574BE1-E371-1B4B-B060-7C05A2AF2813}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/chartsheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{0102EC28-5A40-9149-9A86-871BEFCE7A14}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/chartsheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{7AC78F53-FA8D-9D48-B5AF-D2B263F88E29}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8670774" cy="6281964"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9ED0314-4F9A-47FF-8C72-53F1477AF46C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8669514" cy="6279444"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D45743CA-E8E6-778B-F8C8-6C07CB3954C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8670774" cy="6281964"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{017DF2A5-6B0D-EAA7-2E0E-DA9E0B65CF7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1136,71 +5610,71 @@
   <sheetData>
     <row r="1" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
+      <c r="A2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
       <c r="J3" s="3"/>
-      <c r="L3" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="18"/>
-      <c r="S3" s="18"/>
-      <c r="T3" s="18"/>
-      <c r="U3" s="18"/>
-      <c r="V3" s="18"/>
-      <c r="W3" s="18"/>
+      <c r="L3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
     </row>
     <row r="4" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
       <c r="J4" s="3"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="18"/>
-      <c r="V4" s="18"/>
-      <c r="W4" s="18"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="19"/>
     </row>
     <row r="5" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
@@ -1213,18 +5687,18 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18"/>
-      <c r="S5" s="18"/>
-      <c r="T5" s="18"/>
-      <c r="U5" s="18"/>
-      <c r="V5" s="18"/>
-      <c r="W5" s="18"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="19"/>
+      <c r="V5" s="19"/>
+      <c r="W5" s="19"/>
     </row>
     <row r="6" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
@@ -1236,25 +5710,25 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="18"/>
-      <c r="W6" s="18"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
     </row>
     <row r="7" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -1273,10 +5747,10 @@
       </c>
       <c r="J8" s="1"/>
       <c r="L8" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1284,38 +5758,38 @@
         <v>2</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1402,17 +5876,33 @@
       <c r="L11" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
+      <c r="M11" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0.16</v>
+      </c>
+      <c r="O11" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="P11" s="10">
+        <v>0.88</v>
+      </c>
       <c r="R11" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
+      <c r="S11" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="T11" s="10">
+        <v>0.53</v>
+      </c>
+      <c r="U11" s="10">
+        <v>0.45</v>
+      </c>
+      <c r="V11" s="10">
+        <v>0.56999999999999995</v>
+      </c>
     </row>
     <row r="12" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
@@ -1444,17 +5934,33 @@
       <c r="L12" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
+      <c r="M12" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="O12" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="P12" s="10">
+        <v>0.3</v>
+      </c>
       <c r="R12" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
+      <c r="S12" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="T12" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="U12" s="10">
+        <v>0.51</v>
+      </c>
+      <c r="V12" s="10">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="13" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
@@ -1486,33 +5992,65 @@
       <c r="L13" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
+      <c r="M13" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="O13" s="10">
+        <v>0.18</v>
+      </c>
+      <c r="P13" s="10">
+        <v>0.41</v>
+      </c>
       <c r="R13" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
+      <c r="S13" s="10">
+        <v>0.27</v>
+      </c>
+      <c r="T13" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="U13" s="10">
+        <v>0.24</v>
+      </c>
+      <c r="V13" s="10">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="14" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L14" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
+      <c r="M14" s="10">
+        <v>0</v>
+      </c>
+      <c r="N14" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="O14" s="10">
+        <v>0.22</v>
+      </c>
+      <c r="P14" s="10">
+        <v>0.39</v>
+      </c>
       <c r="R14" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
+      <c r="S14" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="T14" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="U14" s="10">
+        <v>0.46</v>
+      </c>
+      <c r="V14" s="10">
+        <v>0.56000000000000005</v>
+      </c>
     </row>
     <row r="15" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
@@ -1528,40 +6066,40 @@
         <v>2</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L16" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="18"/>
-      <c r="R16" s="18"/>
-      <c r="S16" s="18"/>
-      <c r="T16" s="18"/>
-      <c r="U16" s="18"/>
-      <c r="V16" s="18"/>
+        <v>17</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="19"/>
       <c r="W16" s="12"/>
     </row>
     <row r="17" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1591,17 +6129,17 @@
         <f>G17-H17</f>
         <v>0</v>
       </c>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="18"/>
-      <c r="T17" s="18"/>
-      <c r="U17" s="18"/>
-      <c r="V17" s="18"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="19"/>
+      <c r="V17" s="19"/>
       <c r="W17" s="12"/>
     </row>
     <row r="18" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1667,7 +6205,7 @@
         <v>0.21999999999999975</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1700,10 +6238,10 @@
     </row>
     <row r="23" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -1712,7 +6250,7 @@
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
-      <c r="K23" s="20"/>
+      <c r="K23" s="17"/>
     </row>
     <row r="24" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
@@ -1727,26 +6265,26 @@
         <v>2</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1874,26 +6412,26 @@
         <v>2</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="9" t="s">
         <v>2</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -2035,162 +6573,220 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
+      <c r="A1" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
       <c r="G2" s="13"/>
     </row>
     <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9"/>
       <c r="B5" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
+        <v>32</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
+      <c r="B6">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="C6" s="18">
+        <v>2.81E-2</v>
+      </c>
+      <c r="D6" s="10">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
+      <c r="B7" s="10">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="C7" s="18">
+        <v>1.77E-2</v>
+      </c>
+      <c r="D7" s="10">
+        <v>2.35E-2</v>
+      </c>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
+      <c r="B8" s="10">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="C8" s="18">
+        <v>1.77E-2</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2.5899999999999999E-2</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
+      <c r="B9" s="10">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="C9" s="18">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="D9" s="10">
+        <v>3.0300000000000001E-2</v>
+      </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="11">
+        <f>AVERAGE(B6:B9)</f>
+        <v>1.9624999999999997E-2</v>
+      </c>
+      <c r="C10" s="11">
+        <f>AVERAGE(C6:C9)</f>
+        <v>2.0150000000000001E-2</v>
+      </c>
+      <c r="D10" s="11">
+        <f>AVERAGE(D6:D9)</f>
+        <v>2.7949999999999996E-2</v>
+      </c>
       <c r="F10" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+        <v>8</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="H10" s="11">
+        <v>1E-3</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
+      <c r="B11" s="11">
+        <f>_xlfn.STDEV.P(B6:B9)</f>
+        <v>5.3560713214071418E-4</v>
+      </c>
+      <c r="C11" s="11">
+        <f>_xlfn.STDEV.P(C6:C9)</f>
+        <v>4.5964660338133597E-3</v>
+      </c>
+      <c r="D11" s="11">
+        <f>_xlfn.STDEV.P(D6:D9)</f>
+        <v>3.4186985827943349E-3</v>
+      </c>
       <c r="F11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
+        <v>31</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="H11" s="11">
+        <v>5.0000000000000001E-3</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="15">
+        <f>_xlfn.T.TEST(C6:C9,B6:B9,1,1)</f>
+        <v>0.41911660424008312</v>
+      </c>
+      <c r="D12" s="15">
+        <f>_xlfn.T.TEST(D6:D9,B6:B9,1,1)</f>
+        <v>1.0405513615772499E-2</v>
+      </c>
       <c r="F12" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+        <v>32</v>
+      </c>
+      <c r="G12" s="11">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="H12" s="11">
+        <v>3.0000000000000001E-3</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
+      <c r="A14" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
     </row>
     <row r="15" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
     </row>
     <row r="16" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
     </row>
     <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="3">
